--- a/data-preprocessing/rpc-footprints/Codes/RPC to SUA.xlsx
+++ b/data-preprocessing/rpc-footprints/Codes/RPC to SUA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wilhelmwanecek/dev/safad-scripts/Codes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wilhelmwanecek/dev/safad/data-preprocessing/rpc-footprints/Codes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8663A977-6318-A14F-97B7-6F7DED6193AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F02BAE-CA24-474C-A493-C2E6635C721D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="26540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2734" uniqueCount="1557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2738" uniqueCount="1556">
   <si>
     <t>FoodEx2 Code</t>
   </si>
@@ -1849,12 +1848,6 @@
     <t>Gooseberries (green, red and yellow)</t>
   </si>
   <si>
-    <t>01351.02</t>
-  </si>
-  <si>
-    <t>Gooseberries</t>
-  </si>
-  <si>
     <t>A01LH</t>
   </si>
   <si>
@@ -4312,9 +4305,6 @@
     <t>Watermelons</t>
   </si>
   <si>
-    <t>01221</t>
-  </si>
-  <si>
     <t>watermelons</t>
   </si>
   <si>
@@ -4712,6 +4702,12 @@
   </si>
   <si>
     <t>Deer liver</t>
+  </si>
+  <si>
+    <t>Bytte från 01221 (watermelons) till cantaloups and other melons</t>
+  </si>
+  <si>
+    <t>Bytt från 01355.02 Gooseberries</t>
   </si>
 </sst>
 </file>
@@ -4940,7 +4936,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -5054,9 +5050,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -5618,13 +5611,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>1277</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>1279</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>201</v>
@@ -5641,10 +5634,10 @@
         <v>398</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>201</v>
@@ -5658,19 +5651,19 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>827</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="D7" s="15" t="s">
         <v>828</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="E7" t="s">
         <v>829</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>830</v>
-      </c>
-      <c r="E7" t="s">
-        <v>831</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -5678,19 +5671,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="D8" s="15" t="s">
         <v>699</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="E8" t="s">
         <v>700</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>701</v>
-      </c>
-      <c r="E8" t="s">
-        <v>702</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -5698,19 +5691,19 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>1145</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>1146</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>1147</v>
-      </c>
       <c r="D9" s="15" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E9" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -5718,19 +5711,19 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="37" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C10" s="37" t="s">
         <v>1263</v>
       </c>
-      <c r="B10" s="37" t="s">
+      <c r="D10" s="36" t="s">
         <v>1264</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="E10" s="37" t="s">
         <v>1265</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>1266</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>1267</v>
       </c>
       <c r="F10" s="37"/>
     </row>
@@ -5756,19 +5749,19 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>1161</v>
       </c>
-      <c r="B12" s="49" t="s">
+      <c r="D12" s="15" t="s">
         <v>1162</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="E12" t="s">
         <v>1163</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>1164</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1165</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -5776,19 +5769,19 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>933</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="D13" s="15" t="s">
         <v>934</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="E13" t="s">
         <v>935</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>936</v>
-      </c>
-      <c r="E13" t="s">
-        <v>937</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -5816,13 +5809,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="37" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B15" s="37" t="s">
         <v>386</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>388</v>
@@ -5832,7 +5825,7 @@
       </c>
       <c r="F15" s="37"/>
       <c r="H15" s="43" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="I15" s="37"/>
     </row>
@@ -5858,19 +5851,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>1113</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="D17" s="15" t="s">
         <v>1114</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="E17" s="2" t="s">
         <v>1115</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>1117</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -5958,13 +5951,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>652</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>654</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>191</v>
@@ -5978,13 +5971,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>715</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>717</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>191</v>
@@ -5998,13 +5991,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>723</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>725</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>191</v>
@@ -6018,13 +6011,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>742</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>744</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>191</v>
@@ -6038,13 +6031,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>1121</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>1123</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>191</v>
@@ -6058,13 +6051,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>1152</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>1154</v>
       </c>
       <c r="D27" s="15" t="s">
         <v>191</v>
@@ -6078,13 +6071,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>1325</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>1327</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>191</v>
@@ -6098,13 +6091,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>1417</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>1419</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>191</v>
@@ -6198,13 +6191,13 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>655</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>657</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>432</v>
@@ -6218,13 +6211,13 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>739</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>741</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>432</v>
@@ -6238,13 +6231,13 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>432</v>
@@ -6301,13 +6294,13 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>1100</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>1102</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>396</v>
@@ -6321,13 +6314,13 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>1280</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>1282</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>396</v>
@@ -6362,39 +6355,42 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>1420</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="D42" s="15" t="s">
+        <v>858</v>
+      </c>
+      <c r="E42" t="s">
         <v>1421</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>1422</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>1423</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1424</v>
-      </c>
       <c r="F42" t="s">
         <v>18</v>
+      </c>
+      <c r="H42" s="44" t="s">
+        <v>1554</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="D43" s="15" t="s">
         <v>858</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="E43" t="s">
         <v>859</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>860</v>
-      </c>
-      <c r="E43" t="s">
-        <v>861</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -6443,13 +6439,13 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>1333</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>1335</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>320</v>
@@ -6485,10 +6481,10 @@
       <c r="A48" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="B48" s="49" t="s">
+      <c r="B48" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="C48" s="49" t="s">
+      <c r="C48" s="4" t="s">
         <v>567</v>
       </c>
       <c r="D48" s="15" t="s">
@@ -6543,13 +6539,13 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>615</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>617</v>
       </c>
       <c r="D51" s="15" t="s">
         <v>36</v>
@@ -6565,10 +6561,10 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>37</v>
@@ -6577,7 +6573,7 @@
         <v>36</v>
       </c>
       <c r="E52" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="F52" t="s">
         <v>18</v>
@@ -6605,13 +6601,13 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>1097</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>1099</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>410</v>
@@ -6625,19 +6621,19 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>1024</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="D55" s="15" t="s">
         <v>1025</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="E55" s="5" t="s">
         <v>1026</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>1027</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>1028</v>
       </c>
       <c r="F55" t="s">
         <v>18</v>
@@ -6767,13 +6763,13 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>692</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>694</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>63</v>
@@ -6787,13 +6783,13 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>991</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>992</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>993</v>
       </c>
       <c r="D63" s="15" t="s">
         <v>63</v>
@@ -6807,13 +6803,13 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>994</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>995</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>996</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>63</v>
@@ -6827,13 +6823,13 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>1395</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>1396</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>1397</v>
       </c>
       <c r="D65" s="15" t="s">
         <v>63</v>
@@ -6887,13 +6883,13 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>950</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>951</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>952</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>330</v>
@@ -6907,13 +6903,13 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>1225</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>1227</v>
       </c>
       <c r="D69" s="15" t="s">
         <v>330</v>
@@ -6927,13 +6923,13 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>1291</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>1293</v>
       </c>
       <c r="D70" s="15" t="s">
         <v>330</v>
@@ -6947,19 +6943,19 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="D71" s="15" t="s">
         <v>752</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="E71" t="s">
         <v>753</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>754</v>
-      </c>
-      <c r="E71" t="s">
-        <v>755</v>
       </c>
       <c r="F71" t="s">
         <v>18</v>
@@ -7033,13 +7029,13 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>683</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>685</v>
       </c>
       <c r="D75" s="15" t="s">
         <v>275</v>
@@ -7055,13 +7051,13 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>892</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>893</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>894</v>
       </c>
       <c r="D76" s="15" t="s">
         <v>275</v>
@@ -7077,13 +7073,13 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="28" t="s">
+        <v>964</v>
+      </c>
+      <c r="B77" s="28" t="s">
+        <v>965</v>
+      </c>
+      <c r="C77" s="28" t="s">
         <v>966</v>
-      </c>
-      <c r="B77" s="28" t="s">
-        <v>967</v>
-      </c>
-      <c r="C77" s="28" t="s">
-        <v>968</v>
       </c>
       <c r="D77" s="15" t="s">
         <v>275</v>
@@ -7099,13 +7095,13 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>1171</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>1173</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>275</v>
@@ -7121,13 +7117,13 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>1242</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>1244</v>
       </c>
       <c r="D79" s="15" t="s">
         <v>275</v>
@@ -7143,13 +7139,13 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>1380</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>1382</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>275</v>
@@ -7165,19 +7161,19 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>1328</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="D81" s="15" t="s">
         <v>1329</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="E81" t="s">
         <v>1330</v>
-      </c>
-      <c r="D81" s="15" t="s">
-        <v>1331</v>
-      </c>
-      <c r="E81" t="s">
-        <v>1332</v>
       </c>
       <c r="F81" t="s">
         <v>18</v>
@@ -7265,13 +7261,13 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>895</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>896</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>897</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>526</v>
@@ -7287,19 +7283,19 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="D87" s="15" t="s">
         <v>619</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="E87" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>621</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="F87" t="s">
         <v>18</v>
@@ -7307,19 +7303,19 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="B88" s="4" t="s">
-        <v>841</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>842</v>
-      </c>
       <c r="D88" s="15" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="F88" t="s">
         <v>18</v>
@@ -7327,19 +7323,19 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>984</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="D89" s="15" t="s">
         <v>985</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>986</v>
-      </c>
-      <c r="D89" s="15" t="s">
-        <v>987</v>
-      </c>
       <c r="E89" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F89" t="s">
         <v>18</v>
@@ -7347,19 +7343,19 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>985</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>984</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D90" s="15" t="s">
-        <v>987</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>986</v>
       </c>
       <c r="F90" t="s">
         <v>18</v>
@@ -7367,19 +7363,19 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C91" s="4" t="s">
         <v>1061</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="D91" s="15" t="s">
         <v>1062</v>
       </c>
-      <c r="C91" s="4" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D91" s="15" t="s">
-        <v>1064</v>
-      </c>
       <c r="E91" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="F91" t="s">
         <v>18</v>
@@ -7387,19 +7383,19 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="D92" s="15" t="s">
         <v>611</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="E92" s="5" t="s">
         <v>612</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>613</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>614</v>
       </c>
       <c r="F92" t="s">
         <v>18</v>
@@ -7410,16 +7406,16 @@
     <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" s="28"/>
       <c r="B93" s="28" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C93" s="28" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E93" s="29" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F93" t="s">
         <v>18</v>
@@ -7429,19 +7425,19 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="D94" s="15" t="s">
         <v>735</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="E94" s="5" t="s">
         <v>736</v>
-      </c>
-      <c r="D94" s="15" t="s">
-        <v>737</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>738</v>
       </c>
       <c r="F94" t="s">
         <v>18</v>
@@ -7449,19 +7445,19 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>758</v>
-      </c>
       <c r="D95" s="15" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="F95" t="s">
         <v>18</v>
@@ -7471,19 +7467,19 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="B96" s="4" t="s">
-        <v>768</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>769</v>
-      </c>
       <c r="D96" s="15" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="F96" t="s">
         <v>18</v>
@@ -7493,19 +7489,19 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>956</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="D97" s="15" t="s">
         <v>957</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>958</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>959</v>
-      </c>
       <c r="E97" s="5" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="F97" t="s">
         <v>18</v>
@@ -7515,19 +7511,19 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="D98" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="E98" s="5" t="s">
         <v>837</v>
-      </c>
-      <c r="D98" s="15" t="s">
-        <v>838</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>839</v>
       </c>
       <c r="F98" t="s">
         <v>18</v>
@@ -7537,19 +7533,19 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>1344</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="D99" s="15" t="s">
         <v>1345</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="E99" s="5" t="s">
         <v>1346</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>1347</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>1348</v>
       </c>
       <c r="F99" t="s">
         <v>18</v>
@@ -7559,19 +7555,19 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="F100" t="s">
         <v>18</v>
@@ -7603,13 +7599,13 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C102" s="4" t="s">
         <v>1260</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>1261</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>1262</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>55</v>
@@ -7625,19 +7621,19 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C103" s="4" t="s">
         <v>920</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="D103" s="15" t="s">
         <v>921</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="E103" s="5" t="s">
         <v>922</v>
-      </c>
-      <c r="D103" s="15" t="s">
-        <v>923</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>924</v>
       </c>
       <c r="F103" t="s">
         <v>18</v>
@@ -7647,19 +7643,19 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="F104" t="s">
         <v>18</v>
@@ -7669,19 +7665,19 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C105" s="4" t="s">
         <v>1109</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="D105" s="15" t="s">
         <v>1110</v>
       </c>
-      <c r="C105" s="4" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D105" s="15" t="s">
-        <v>1112</v>
-      </c>
       <c r="E105" s="5" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F105" t="s">
         <v>18</v>
@@ -7713,19 +7709,19 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C107" s="4" t="s">
         <v>1268</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="D107" s="15" t="s">
         <v>1269</v>
       </c>
-      <c r="C107" s="4" t="s">
-        <v>1270</v>
-      </c>
-      <c r="D107" s="15" t="s">
-        <v>1271</v>
-      </c>
       <c r="E107" s="5" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="F107" t="s">
         <v>18</v>
@@ -7757,19 +7753,19 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C109" s="4" t="s">
         <v>1005</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="D109" s="15" t="s">
         <v>1006</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="E109" s="5" t="s">
         <v>1007</v>
-      </c>
-      <c r="D109" s="15" t="s">
-        <v>1008</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>1009</v>
       </c>
       <c r="F109" t="s">
         <v>18</v>
@@ -7823,13 +7819,13 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="C112" s="4" t="s">
         <v>885</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>886</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>887</v>
       </c>
       <c r="D112" s="15" t="s">
         <v>458</v>
@@ -7845,13 +7841,13 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C113" s="4" t="s">
         <v>1077</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>1079</v>
       </c>
       <c r="D113" s="15" t="s">
         <v>458</v>
@@ -7911,13 +7907,13 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>1209</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>1210</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>1211</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>449</v>
@@ -7942,32 +7938,35 @@
         <v>601</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>602</v>
+        <v>91</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>603</v>
+        <v>144</v>
       </c>
       <c r="F117" t="s">
         <v>18</v>
+      </c>
+      <c r="H117" s="44" t="s">
+        <v>1555</v>
       </c>
       <c r="N117" s="7"/>
       <c r="O117" s="2"/>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="C118" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="D118" s="15" t="s">
         <v>719</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="E118" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="D118" s="15" t="s">
-        <v>721</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>722</v>
       </c>
       <c r="F118" t="s">
         <v>18</v>
@@ -8019,13 +8018,13 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C121" s="4" t="s">
         <v>1129</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>1131</v>
       </c>
       <c r="D121" s="15" t="s">
         <v>143</v>
@@ -8041,19 +8040,19 @@
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C122" s="4" t="s">
         <v>1298</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="D122" s="15" t="s">
         <v>1299</v>
       </c>
-      <c r="C122" s="4" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D122" s="15" t="s">
-        <v>1301</v>
-      </c>
       <c r="E122" s="5" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="F122" t="s">
         <v>18</v>
@@ -8164,18 +8163,20 @@
       <c r="E127" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F127" s="37"/>
-      <c r="I127" s="44" t="s">
+      <c r="F127" t="s">
+        <v>18</v>
+      </c>
+      <c r="H127" s="44" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" s="28"/>
       <c r="B128" s="28" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C128" s="28" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D128" s="15" t="s">
         <v>91</v>
@@ -8192,10 +8193,10 @@
     <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" s="28"/>
       <c r="B129" s="28" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C129" s="28" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D129" s="15" t="s">
         <v>91</v>
@@ -8211,44 +8212,46 @@
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="C130" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="D130" s="36" t="s">
         <v>710</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="E130" s="37" t="s">
         <v>711</v>
       </c>
-      <c r="D130" s="36" t="s">
+      <c r="F130" t="s">
+        <v>18</v>
+      </c>
+      <c r="H130" s="44" t="s">
         <v>712</v>
-      </c>
-      <c r="E130" s="37" t="s">
-        <v>713</v>
-      </c>
-      <c r="F130" t="s">
-        <v>18</v>
-      </c>
-      <c r="H130" s="44" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" s="37" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B131" s="37" t="s">
+        <v>708</v>
+      </c>
+      <c r="C131" s="37" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D131" s="36" t="s">
         <v>710</v>
       </c>
-      <c r="C131" s="37" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D131" s="36" t="s">
-        <v>712</v>
-      </c>
       <c r="E131" s="37" t="s">
-        <v>713</v>
-      </c>
-      <c r="F131" s="37"/>
+        <v>711</v>
+      </c>
+      <c r="F131" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
@@ -8333,13 +8336,13 @@
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="C136" s="4" t="s">
         <v>604</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>606</v>
       </c>
       <c r="D136" s="15" t="s">
         <v>96</v>
@@ -8353,13 +8356,13 @@
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="C137" s="4" t="s">
         <v>607</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>609</v>
       </c>
       <c r="D137" s="15" t="s">
         <v>96</v>
@@ -8376,13 +8379,13 @@
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="C138" s="4" t="s">
         <v>781</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>782</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>783</v>
       </c>
       <c r="D138" s="15" t="s">
         <v>96</v>
@@ -8396,13 +8399,13 @@
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="C139" s="4" t="s">
         <v>794</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>795</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>796</v>
       </c>
       <c r="D139" s="15" t="s">
         <v>96</v>
@@ -8416,13 +8419,13 @@
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>797</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>798</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>799</v>
       </c>
       <c r="D140" s="15" t="s">
         <v>96</v>
@@ -8438,13 +8441,13 @@
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C141" s="4" t="s">
         <v>854</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>855</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>856</v>
       </c>
       <c r="D141" s="15" t="s">
         <v>96</v>
@@ -8460,13 +8463,13 @@
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>942</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>943</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>944</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>96</v>
@@ -8480,13 +8483,13 @@
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C143" s="4" t="s">
         <v>953</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>954</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>955</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>96</v>
@@ -8500,13 +8503,13 @@
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="C144" s="4" t="s">
         <v>973</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>974</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>975</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>96</v>
@@ -8525,13 +8528,13 @@
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="C145" s="4" t="s">
         <v>1000</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>1002</v>
       </c>
       <c r="D145" s="15" t="s">
         <v>96</v>
@@ -8545,13 +8548,13 @@
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>1091</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>1093</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>96</v>
@@ -8565,13 +8568,13 @@
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="D147" s="15" t="s">
         <v>96</v>
@@ -8629,13 +8632,13 @@
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="C150" s="4" t="s">
         <v>812</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>813</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>814</v>
       </c>
       <c r="D150" s="15" t="s">
         <v>31</v>
@@ -8654,13 +8657,13 @@
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C151" s="4" t="s">
         <v>1029</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>1031</v>
       </c>
       <c r="D151" s="15" t="s">
         <v>31</v>
@@ -8679,13 +8682,13 @@
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C152" s="4" t="s">
         <v>1058</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>1060</v>
       </c>
       <c r="D152" s="15" t="s">
         <v>31</v>
@@ -8750,19 +8753,19 @@
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="D155" s="15" t="s">
         <v>648</v>
       </c>
-      <c r="C155" s="4" t="s">
+      <c r="E155" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="D155" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="F155" t="s">
         <v>18</v>
@@ -8772,65 +8775,65 @@
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C156" s="4" t="s">
         <v>1065</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="D156" s="36" t="s">
         <v>1066</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="E156" s="37" t="s">
         <v>1067</v>
       </c>
-      <c r="D156" s="36" t="s">
+      <c r="F156" t="s">
+        <v>18</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>1068</v>
       </c>
-      <c r="E156" s="37" t="s">
+      <c r="I156" s="44" t="s">
         <v>1069</v>
-      </c>
-      <c r="F156" t="s">
-        <v>18</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>1070</v>
-      </c>
-      <c r="I156" s="44" t="s">
-        <v>1071</v>
       </c>
       <c r="N156" s="7"/>
       <c r="O156" s="5"/>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A157" s="37" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B157" s="37" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C157" s="37" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D157" s="36" t="s">
         <v>1066</v>
       </c>
-      <c r="C157" s="37" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D157" s="36" t="s">
-        <v>1068</v>
-      </c>
       <c r="E157" s="37" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="F157" s="37"/>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C158" s="4" t="s">
         <v>1407</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="D158" s="15" t="s">
         <v>1408</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="E158" s="5" t="s">
         <v>1409</v>
-      </c>
-      <c r="D158" s="15" t="s">
-        <v>1410</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>1411</v>
       </c>
       <c r="F158" t="s">
         <v>18</v>
@@ -8862,37 +8865,37 @@
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A160" s="37" t="s">
+        <v>724</v>
+      </c>
+      <c r="B160" s="37" t="s">
+        <v>725</v>
+      </c>
+      <c r="C160" s="37" t="s">
         <v>726</v>
       </c>
-      <c r="B160" s="37" t="s">
+      <c r="D160" s="36" t="s">
         <v>727</v>
       </c>
-      <c r="C160" s="37" t="s">
+      <c r="E160" s="37" t="s">
         <v>728</v>
-      </c>
-      <c r="D160" s="36" t="s">
-        <v>729</v>
-      </c>
-      <c r="E160" s="37" t="s">
-        <v>730</v>
       </c>
       <c r="F160" s="37"/>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C161" s="4" t="s">
         <v>1272</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="D161" s="15" t="s">
         <v>1273</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="E161" s="5" t="s">
         <v>1274</v>
-      </c>
-      <c r="D161" s="15" t="s">
-        <v>1275</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>1276</v>
       </c>
       <c r="F161" t="s">
         <v>18</v>
@@ -8902,19 +8905,19 @@
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C162" s="4" t="s">
         <v>1010</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="D162" s="15" t="s">
         <v>1011</v>
       </c>
-      <c r="C162" s="4" t="s">
+      <c r="E162" s="2" t="s">
         <v>1012</v>
-      </c>
-      <c r="D162" s="15" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>1014</v>
       </c>
       <c r="F162" t="s">
         <v>18</v>
@@ -8924,19 +8927,19 @@
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="C163" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="D163" s="15" t="s">
         <v>773</v>
       </c>
-      <c r="C163" s="4" t="s">
+      <c r="E163" s="5" t="s">
         <v>774</v>
-      </c>
-      <c r="D163" s="15" t="s">
-        <v>775</v>
-      </c>
-      <c r="E163" s="5" t="s">
-        <v>776</v>
       </c>
       <c r="F163" t="s">
         <v>18</v>
@@ -8946,19 +8949,19 @@
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" s="28" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B164" s="28" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C164" s="21" t="s">
         <v>1124</v>
       </c>
-      <c r="B164" s="28" t="s">
+      <c r="D164" s="15" t="s">
         <v>1125</v>
       </c>
-      <c r="C164" s="21" t="s">
+      <c r="E164" s="28" t="s">
         <v>1126</v>
-      </c>
-      <c r="D164" s="15" t="s">
-        <v>1127</v>
-      </c>
-      <c r="E164" s="28" t="s">
-        <v>1128</v>
       </c>
       <c r="F164" t="s">
         <v>18</v>
@@ -9008,13 +9011,13 @@
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C167" s="4" t="s">
         <v>1181</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>1183</v>
       </c>
       <c r="D167" s="15" t="s">
         <v>227</v>
@@ -9028,19 +9031,19 @@
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C168" s="4" t="s">
         <v>1321</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>1322</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>1323</v>
       </c>
       <c r="D168" s="15" t="s">
         <v>227</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="F168" t="s">
         <v>18</v>
@@ -9050,19 +9053,19 @@
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C169" s="4" t="s">
         <v>1082</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="D169" s="15" t="s">
         <v>1083</v>
       </c>
-      <c r="C169" s="4" t="s">
+      <c r="E169" s="5" t="s">
         <v>1084</v>
-      </c>
-      <c r="D169" s="15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E169" s="5" t="s">
-        <v>1086</v>
       </c>
       <c r="F169" t="s">
         <v>18</v>
@@ -9072,19 +9075,19 @@
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="C170" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="D170" s="15" t="s">
         <v>659</v>
       </c>
-      <c r="C170" s="4" t="s">
+      <c r="E170" s="5" t="s">
         <v>660</v>
-      </c>
-      <c r="D170" s="15" t="s">
-        <v>661</v>
-      </c>
-      <c r="E170" s="5" t="s">
-        <v>662</v>
       </c>
       <c r="F170" t="s">
         <v>18</v>
@@ -9094,61 +9097,61 @@
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" s="37" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B171" s="37" t="s">
+        <v>657</v>
+      </c>
+      <c r="C171" s="37" t="s">
+        <v>661</v>
+      </c>
+      <c r="D171" s="15" t="s">
         <v>659</v>
       </c>
-      <c r="C171" s="37" t="s">
-        <v>663</v>
-      </c>
-      <c r="D171" s="15" t="s">
-        <v>661</v>
-      </c>
       <c r="E171" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F171" s="37"/>
       <c r="H171" s="44" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" s="37" t="s">
+        <v>909</v>
+      </c>
+      <c r="B172" s="37" t="s">
+        <v>910</v>
+      </c>
+      <c r="C172" s="37" t="s">
         <v>911</v>
       </c>
-      <c r="B172" s="37" t="s">
-        <v>912</v>
-      </c>
-      <c r="C172" s="37" t="s">
-        <v>913</v>
-      </c>
       <c r="D172" s="15" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F172" s="37"/>
       <c r="H172" s="44" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F173" t="s">
         <v>18</v>
@@ -9158,19 +9161,19 @@
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="C174" s="4" t="s">
         <v>963</v>
       </c>
-      <c r="B174" s="4" t="s">
-        <v>964</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>965</v>
-      </c>
       <c r="D174" s="15" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F174" t="s">
         <v>18</v>
@@ -9180,19 +9183,19 @@
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C175" s="4" t="s">
         <v>1094</v>
       </c>
-      <c r="B175" s="4" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>1096</v>
-      </c>
       <c r="D175" s="15" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F175" t="s">
         <v>18</v>
@@ -9202,40 +9205,40 @@
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" s="37" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B176" s="37" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C176" s="37" t="s">
         <v>1220</v>
       </c>
-      <c r="B176" s="37" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C176" s="37" t="s">
-        <v>1222</v>
-      </c>
       <c r="D176" s="15" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F176" s="37"/>
       <c r="H176" s="44" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F177" t="s">
         <v>18</v>
@@ -9245,19 +9248,19 @@
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="C178" s="4" t="s">
         <v>945</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="D178" s="15" t="s">
         <v>946</v>
       </c>
-      <c r="C178" s="4" t="s">
+      <c r="E178" s="5" t="s">
         <v>947</v>
-      </c>
-      <c r="D178" s="15" t="s">
-        <v>948</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>949</v>
       </c>
       <c r="F178" t="s">
         <v>18</v>
@@ -9267,19 +9270,19 @@
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C179" s="4" t="s">
         <v>1349</v>
       </c>
-      <c r="B179" s="4" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>1351</v>
-      </c>
       <c r="D179" s="15" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="F179" t="s">
         <v>18</v>
@@ -9310,16 +9313,16 @@
     <row r="181" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A181" s="28"/>
       <c r="B181" s="28" t="s">
+        <v>978</v>
+      </c>
+      <c r="C181" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="D181" s="15" t="s">
         <v>980</v>
       </c>
-      <c r="C181" s="28" t="s">
+      <c r="E181" s="29" t="s">
         <v>981</v>
-      </c>
-      <c r="D181" s="15" t="s">
-        <v>982</v>
-      </c>
-      <c r="E181" s="29" t="s">
-        <v>983</v>
       </c>
       <c r="F181" t="s">
         <v>18</v>
@@ -9330,16 +9333,16 @@
     <row r="182" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A182" s="28"/>
       <c r="B182" s="28" t="s">
+        <v>974</v>
+      </c>
+      <c r="C182" s="28" t="s">
+        <v>975</v>
+      </c>
+      <c r="D182" s="15" t="s">
         <v>976</v>
       </c>
-      <c r="C182" s="28" t="s">
+      <c r="E182" s="29" t="s">
         <v>977</v>
-      </c>
-      <c r="D182" s="15" t="s">
-        <v>978</v>
-      </c>
-      <c r="E182" s="29" t="s">
-        <v>979</v>
       </c>
       <c r="F182" t="s">
         <v>18</v>
@@ -9349,19 +9352,19 @@
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="C183" s="4" t="s">
         <v>822</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="D183" s="15" t="s">
         <v>823</v>
       </c>
-      <c r="C183" s="4" t="s">
+      <c r="E183" s="5" t="s">
         <v>824</v>
-      </c>
-      <c r="D183" s="15" t="s">
-        <v>825</v>
-      </c>
-      <c r="E183" s="5" t="s">
-        <v>826</v>
       </c>
       <c r="F183" t="s">
         <v>18</v>
@@ -9371,19 +9374,19 @@
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A184" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C184" s="4" t="s">
         <v>925</v>
       </c>
-      <c r="B184" s="4" t="s">
-        <v>926</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>927</v>
-      </c>
       <c r="D184" s="15" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="F184" t="s">
         <v>18</v>
@@ -9393,19 +9396,19 @@
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C185" s="4" t="s">
         <v>1336</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="D185" s="15" t="s">
         <v>1337</v>
       </c>
-      <c r="C185" s="4" t="s">
-        <v>1338</v>
-      </c>
-      <c r="D185" s="15" t="s">
-        <v>1339</v>
-      </c>
       <c r="E185" s="2" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="F185" t="s">
         <v>18</v>
@@ -9480,13 +9483,13 @@
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="C189" s="4" t="s">
         <v>703</v>
-      </c>
-      <c r="B189" s="4" t="s">
-        <v>704</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>705</v>
       </c>
       <c r="D189" s="15" t="s">
         <v>252</v>
@@ -9502,13 +9505,13 @@
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A190" s="4" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="D190" s="15" t="s">
         <v>252</v>
@@ -9524,13 +9527,13 @@
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B191" s="4" t="s">
         <v>1465</v>
       </c>
-      <c r="B191" s="4" t="s">
-        <v>1468</v>
-      </c>
       <c r="C191" s="4" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="D191" s="15" t="s">
         <v>252</v>
@@ -9568,37 +9571,37 @@
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A193" s="37" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B193" s="37" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C193" s="37" t="s">
         <v>1362</v>
       </c>
-      <c r="B193" s="37" t="s">
+      <c r="D193" s="36" t="s">
         <v>1363</v>
       </c>
-      <c r="C193" s="37" t="s">
+      <c r="E193" s="37" t="s">
         <v>1364</v>
-      </c>
-      <c r="D193" s="36" t="s">
-        <v>1365</v>
-      </c>
-      <c r="E193" s="37" t="s">
-        <v>1366</v>
       </c>
       <c r="F193" s="37"/>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194" s="37" t="s">
+        <v>847</v>
+      </c>
+      <c r="B194" s="37" t="s">
+        <v>848</v>
+      </c>
+      <c r="C194" s="37" t="s">
         <v>849</v>
       </c>
-      <c r="B194" s="37" t="s">
+      <c r="D194" s="36" t="s">
         <v>850</v>
       </c>
-      <c r="C194" s="37" t="s">
+      <c r="E194" s="37" t="s">
         <v>851</v>
-      </c>
-      <c r="D194" s="36" t="s">
-        <v>852</v>
-      </c>
-      <c r="E194" s="37" t="s">
-        <v>853</v>
       </c>
       <c r="F194" s="37"/>
     </row>
@@ -10196,13 +10199,13 @@
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="C222" s="4" t="s">
         <v>706</v>
-      </c>
-      <c r="B222" s="4" t="s">
-        <v>707</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>708</v>
       </c>
       <c r="D222" s="15" t="s">
         <v>26</v>
@@ -10217,13 +10220,13 @@
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C223" s="4" t="s">
         <v>731</v>
-      </c>
-      <c r="B223" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="C223" s="4" t="s">
-        <v>733</v>
       </c>
       <c r="D223" s="15" t="s">
         <v>26</v>
@@ -10242,13 +10245,13 @@
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="C224" s="4" t="s">
         <v>745</v>
-      </c>
-      <c r="B224" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>747</v>
       </c>
       <c r="D224" s="15" t="s">
         <v>26</v>
@@ -10266,13 +10269,13 @@
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="C225" s="4" t="s">
         <v>748</v>
-      </c>
-      <c r="B225" s="4" t="s">
-        <v>749</v>
-      </c>
-      <c r="C225" s="4" t="s">
-        <v>750</v>
       </c>
       <c r="D225" s="15" t="s">
         <v>26</v>
@@ -10291,13 +10294,13 @@
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="C226" s="4" t="s">
         <v>800</v>
-      </c>
-      <c r="B226" s="4" t="s">
-        <v>801</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>802</v>
       </c>
       <c r="D226" s="15" t="s">
         <v>26</v>
@@ -10311,13 +10314,13 @@
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="C227" s="4" t="s">
         <v>815</v>
-      </c>
-      <c r="B227" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>817</v>
       </c>
       <c r="D227" s="15" t="s">
         <v>26</v>
@@ -10332,13 +10335,13 @@
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="C228" s="4" t="s">
         <v>846</v>
-      </c>
-      <c r="B228" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>848</v>
       </c>
       <c r="D228" s="15" t="s">
         <v>26</v>
@@ -10352,13 +10355,13 @@
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="C229" s="4" t="s">
         <v>881</v>
-      </c>
-      <c r="B229" s="4" t="s">
-        <v>882</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>883</v>
       </c>
       <c r="D229" s="15" t="s">
         <v>26</v>
@@ -10374,13 +10377,13 @@
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="C230" s="4" t="s">
         <v>881</v>
-      </c>
-      <c r="B230" s="4" t="s">
-        <v>884</v>
-      </c>
-      <c r="C230" s="4" t="s">
-        <v>883</v>
       </c>
       <c r="D230" s="15" t="s">
         <v>26</v>
@@ -10394,13 +10397,13 @@
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231" s="37" t="s">
+        <v>926</v>
+      </c>
+      <c r="B231" s="37" t="s">
+        <v>927</v>
+      </c>
+      <c r="C231" s="37" t="s">
         <v>928</v>
-      </c>
-      <c r="B231" s="37" t="s">
-        <v>929</v>
-      </c>
-      <c r="C231" s="37" t="s">
-        <v>930</v>
       </c>
       <c r="D231" s="15" t="s">
         <v>26</v>
@@ -10410,18 +10413,18 @@
       </c>
       <c r="F231" s="37"/>
       <c r="H231" s="44" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232" s="4" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D232" s="15" t="s">
         <v>26</v>
@@ -10436,13 +10439,13 @@
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="C233" s="4" t="s">
         <v>960</v>
-      </c>
-      <c r="B233" s="4" t="s">
-        <v>961</v>
-      </c>
-      <c r="C233" s="4" t="s">
-        <v>962</v>
       </c>
       <c r="D233" s="15" t="s">
         <v>26</v>
@@ -10456,13 +10459,13 @@
     </row>
     <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="C234" s="4" t="s">
         <v>988</v>
-      </c>
-      <c r="B234" s="4" t="s">
-        <v>989</v>
-      </c>
-      <c r="C234" s="4" t="s">
-        <v>990</v>
       </c>
       <c r="D234" s="15" t="s">
         <v>26</v>
@@ -10480,13 +10483,13 @@
     </row>
     <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235" s="37" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B235" s="37" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C235" s="37" t="s">
         <v>1032</v>
-      </c>
-      <c r="B235" s="37" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C235" s="37" t="s">
-        <v>1034</v>
       </c>
       <c r="D235" s="15" t="s">
         <v>26</v>
@@ -10496,18 +10499,18 @@
       </c>
       <c r="F235" s="37"/>
       <c r="H235" s="44" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D236" s="15" t="s">
         <v>26</v>
@@ -10522,13 +10525,13 @@
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C237" s="4" t="s">
         <v>1155</v>
-      </c>
-      <c r="B237" s="4" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>1157</v>
       </c>
       <c r="D237" s="15" t="s">
         <v>26</v>
@@ -10544,13 +10547,13 @@
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C238" s="4" t="s">
         <v>1158</v>
-      </c>
-      <c r="B238" s="49" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>1160</v>
       </c>
       <c r="D238" s="15" t="s">
         <v>26</v>
@@ -10569,10 +10572,10 @@
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239" s="28"/>
       <c r="B239" s="28" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C239" s="28" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="D239" s="15" t="s">
         <v>26</v>
@@ -10588,13 +10591,13 @@
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C240" s="4" t="s">
         <v>1168</v>
-      </c>
-      <c r="B240" s="4" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>1170</v>
       </c>
       <c r="D240" s="15" t="s">
         <v>26</v>
@@ -10609,13 +10612,13 @@
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C241" s="4" t="s">
         <v>1174</v>
-      </c>
-      <c r="B241" s="4" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C241" s="4" t="s">
-        <v>1176</v>
       </c>
       <c r="D241" s="15" t="s">
         <v>26</v>
@@ -10633,13 +10636,13 @@
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242" s="4" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C242" s="4" t="s">
         <v>1302</v>
-      </c>
-      <c r="B242" s="4" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C242" s="4" t="s">
-        <v>1304</v>
       </c>
       <c r="D242" s="15" t="s">
         <v>26</v>
@@ -10655,13 +10658,13 @@
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C243" s="4" t="s">
         <v>1352</v>
-      </c>
-      <c r="B243" s="4" t="s">
-        <v>1353</v>
-      </c>
-      <c r="C243" s="4" t="s">
-        <v>1354</v>
       </c>
       <c r="D243" s="15" t="s">
         <v>26</v>
@@ -10676,13 +10679,13 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244" s="4" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C244" s="4" t="s">
         <v>1359</v>
-      </c>
-      <c r="B244" s="4" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C244" s="4" t="s">
-        <v>1361</v>
       </c>
       <c r="D244" s="15" t="s">
         <v>26</v>
@@ -10700,13 +10703,13 @@
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245" s="4" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C245" s="4" t="s">
         <v>1367</v>
-      </c>
-      <c r="B245" s="4" t="s">
-        <v>1368</v>
-      </c>
-      <c r="C245" s="4" t="s">
-        <v>1369</v>
       </c>
       <c r="D245" s="15" t="s">
         <v>26</v>
@@ -10722,13 +10725,13 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C246" s="4" t="s">
         <v>1370</v>
-      </c>
-      <c r="B246" s="4" t="s">
-        <v>1371</v>
-      </c>
-      <c r="C246" s="4" t="s">
-        <v>1372</v>
       </c>
       <c r="D246" s="15" t="s">
         <v>26</v>
@@ -10746,13 +10749,13 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C247" s="4" t="s">
         <v>1392</v>
-      </c>
-      <c r="B247" s="4" t="s">
-        <v>1393</v>
-      </c>
-      <c r="C247" s="4" t="s">
-        <v>1394</v>
       </c>
       <c r="D247" s="15" t="s">
         <v>26</v>
@@ -10767,13 +10770,13 @@
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C248" s="4" t="s">
         <v>1398</v>
-      </c>
-      <c r="B248" s="4" t="s">
-        <v>1399</v>
-      </c>
-      <c r="C248" s="4" t="s">
-        <v>1400</v>
       </c>
       <c r="D248" s="15" t="s">
         <v>26</v>
@@ -10787,13 +10790,13 @@
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249" s="37" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="B249" s="37" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C249" s="37" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="D249" s="15" t="s">
         <v>26</v>
@@ -10803,18 +10806,18 @@
       </c>
       <c r="F249" s="37"/>
       <c r="H249" s="44" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C250" s="4" t="s">
         <v>1404</v>
-      </c>
-      <c r="B250" s="4" t="s">
-        <v>1405</v>
-      </c>
-      <c r="C250" s="4" t="s">
-        <v>1406</v>
       </c>
       <c r="D250" s="15" t="s">
         <v>26</v>
@@ -10833,13 +10836,13 @@
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251" s="4" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="D251" s="15" t="s">
         <v>26</v>
@@ -10917,13 +10920,13 @@
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="C255" s="4" t="s">
         <v>764</v>
-      </c>
-      <c r="B255" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="C255" s="4" t="s">
-        <v>766</v>
       </c>
       <c r="D255" s="15" t="s">
         <v>114</v>
@@ -10939,13 +10942,13 @@
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="C256" s="4" t="s">
         <v>902</v>
-      </c>
-      <c r="B256" s="4" t="s">
-        <v>903</v>
-      </c>
-      <c r="C256" s="4" t="s">
-        <v>904</v>
       </c>
       <c r="D256" s="15" t="s">
         <v>114</v>
@@ -10964,13 +10967,13 @@
     </row>
     <row r="257" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A257" s="4" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D257" s="15" t="s">
         <v>114</v>
@@ -11051,19 +11054,19 @@
     </row>
     <row r="261" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="C261" s="4" t="s">
         <v>759</v>
       </c>
-      <c r="B261" s="4" t="s">
+      <c r="D261" s="15" t="s">
         <v>760</v>
       </c>
-      <c r="C261" s="4" t="s">
+      <c r="E261" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="D261" s="15" t="s">
-        <v>762</v>
-      </c>
-      <c r="E261" s="2" t="s">
-        <v>763</v>
       </c>
       <c r="F261" t="s">
         <v>18</v>
@@ -11095,13 +11098,13 @@
     </row>
     <row r="263" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A263" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C263" s="4" t="s">
         <v>1017</v>
-      </c>
-      <c r="B263" s="4" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C263" s="4" t="s">
-        <v>1019</v>
       </c>
       <c r="D263" s="15" t="s">
         <v>138</v>
@@ -11117,19 +11120,19 @@
     </row>
     <row r="264" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C264" s="4" t="s">
         <v>1020</v>
-      </c>
-      <c r="B264" s="4" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C264" s="4" t="s">
-        <v>1022</v>
       </c>
       <c r="D264" s="15" t="s">
         <v>138</v>
       </c>
       <c r="E264" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="F264" t="s">
         <v>18</v>
@@ -11137,19 +11140,19 @@
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A265" s="37" t="s">
+        <v>805</v>
+      </c>
+      <c r="B265" s="37" t="s">
+        <v>806</v>
+      </c>
+      <c r="C265" s="37" t="s">
         <v>807</v>
       </c>
-      <c r="B265" s="37" t="s">
+      <c r="D265" s="36" t="s">
         <v>808</v>
       </c>
-      <c r="C265" s="37" t="s">
+      <c r="E265" s="37" t="s">
         <v>809</v>
-      </c>
-      <c r="D265" s="36" t="s">
-        <v>810</v>
-      </c>
-      <c r="E265" s="37" t="s">
-        <v>811</v>
       </c>
       <c r="F265" s="37"/>
     </row>
@@ -11217,13 +11220,13 @@
     </row>
     <row r="269" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A269" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C269" s="4" t="s">
         <v>1142</v>
-      </c>
-      <c r="B269" s="4" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C269" s="4" t="s">
-        <v>1144</v>
       </c>
       <c r="D269" s="15" t="s">
         <v>287</v>
@@ -11237,13 +11240,13 @@
     </row>
     <row r="270" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A270" s="41" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B270" s="41" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C270" s="37" t="s">
         <v>1313</v>
-      </c>
-      <c r="B270" s="41" t="s">
-        <v>1314</v>
-      </c>
-      <c r="C270" s="37" t="s">
-        <v>1315</v>
       </c>
       <c r="D270" s="22" t="s">
         <v>287</v>
@@ -11257,19 +11260,19 @@
     </row>
     <row r="271" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A271" s="37" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B271" s="37" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C271" s="37" t="s">
         <v>1316</v>
       </c>
-      <c r="B271" s="37" t="s">
+      <c r="D271" s="36" t="s">
         <v>1317</v>
       </c>
-      <c r="C271" s="37" t="s">
+      <c r="E271" s="37" t="s">
         <v>1318</v>
-      </c>
-      <c r="D271" s="36" t="s">
-        <v>1319</v>
-      </c>
-      <c r="E271" s="37" t="s">
-        <v>1320</v>
       </c>
       <c r="F271" s="35" t="s">
         <v>18</v>
@@ -11337,19 +11340,19 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" s="35" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B275" s="35" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C275" s="35" t="s">
         <v>1412</v>
       </c>
-      <c r="B275" s="35" t="s">
+      <c r="D275" s="36" t="s">
         <v>1413</v>
       </c>
-      <c r="C275" s="35" t="s">
+      <c r="E275" s="37" t="s">
         <v>1414</v>
-      </c>
-      <c r="D275" s="36" t="s">
-        <v>1415</v>
-      </c>
-      <c r="E275" s="37" t="s">
-        <v>1416</v>
       </c>
       <c r="F275" s="35" t="s">
         <v>79</v>
@@ -11357,19 +11360,19 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="35" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B276" s="35" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C276" s="35" t="s">
         <v>1232</v>
       </c>
-      <c r="B276" s="35" t="s">
+      <c r="D276" s="36" t="s">
         <v>1233</v>
       </c>
-      <c r="C276" s="35" t="s">
+      <c r="E276" s="37" t="s">
         <v>1234</v>
-      </c>
-      <c r="D276" s="36" t="s">
-        <v>1235</v>
-      </c>
-      <c r="E276" s="37" t="s">
-        <v>1236</v>
       </c>
       <c r="F276" s="35" t="s">
         <v>79</v>
@@ -11397,19 +11400,19 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="35" t="s">
+        <v>663</v>
+      </c>
+      <c r="B278" s="35" t="s">
+        <v>664</v>
+      </c>
+      <c r="C278" s="35" t="s">
         <v>665</v>
       </c>
-      <c r="B278" s="35" t="s">
+      <c r="D278" s="36" t="s">
         <v>666</v>
       </c>
-      <c r="C278" s="35" t="s">
+      <c r="E278" s="37" t="s">
         <v>667</v>
-      </c>
-      <c r="D278" s="36" t="s">
-        <v>668</v>
-      </c>
-      <c r="E278" s="37" t="s">
-        <v>669</v>
       </c>
       <c r="F278" s="35" t="s">
         <v>79</v>
@@ -11458,13 +11461,13 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="35" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B281" s="35" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C281" s="35" t="s">
         <v>1103</v>
-      </c>
-      <c r="B281" s="35" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C281" s="35" t="s">
-        <v>1105</v>
       </c>
       <c r="D281" s="36" t="s">
         <v>487</v>
@@ -11478,19 +11481,19 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="35" t="s">
+        <v>677</v>
+      </c>
+      <c r="B282" s="35" t="s">
+        <v>678</v>
+      </c>
+      <c r="C282" s="35" t="s">
         <v>679</v>
       </c>
-      <c r="B282" s="35" t="s">
+      <c r="D282" s="36" t="s">
         <v>680</v>
       </c>
-      <c r="C282" s="35" t="s">
-        <v>681</v>
-      </c>
-      <c r="D282" s="36" t="s">
-        <v>682</v>
-      </c>
       <c r="E282" s="37" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F282" s="35" t="s">
         <v>79</v>
@@ -11540,19 +11543,19 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B285" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C285" s="4" t="s">
         <v>1048</v>
       </c>
-      <c r="B285" s="4" t="s">
+      <c r="D285" s="34" t="s">
         <v>1049</v>
       </c>
-      <c r="C285" s="4" t="s">
+      <c r="E285" t="s">
         <v>1050</v>
-      </c>
-      <c r="D285" s="34" t="s">
-        <v>1051</v>
-      </c>
-      <c r="E285" t="s">
-        <v>1052</v>
       </c>
       <c r="F285" s="4" t="s">
         <v>79</v>
@@ -11561,19 +11564,19 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="35" t="s">
+        <v>640</v>
+      </c>
+      <c r="B286" s="35" t="s">
+        <v>641</v>
+      </c>
+      <c r="C286" s="35" t="s">
         <v>642</v>
       </c>
-      <c r="B286" s="35" t="s">
+      <c r="D286" s="36" t="s">
         <v>643</v>
       </c>
-      <c r="C286" s="35" t="s">
+      <c r="E286" s="37" t="s">
         <v>644</v>
-      </c>
-      <c r="D286" s="36" t="s">
-        <v>645</v>
-      </c>
-      <c r="E286" s="37" t="s">
-        <v>646</v>
       </c>
       <c r="F286" s="35" t="s">
         <v>79</v>
@@ -11581,19 +11584,19 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C287" s="4" t="s">
         <v>1118</v>
       </c>
-      <c r="B287" s="4" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C287" s="4" t="s">
-        <v>1120</v>
-      </c>
       <c r="D287" s="15" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E287" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F287" s="4" t="s">
         <v>79</v>
@@ -11601,19 +11604,19 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C288" s="4" t="s">
         <v>1237</v>
       </c>
-      <c r="B288" s="4" t="s">
+      <c r="D288" s="15" t="s">
         <v>1238</v>
       </c>
-      <c r="C288" s="4" t="s">
+      <c r="E288" t="s">
         <v>1239</v>
-      </c>
-      <c r="D288" s="15" t="s">
-        <v>1240</v>
-      </c>
-      <c r="E288" t="s">
-        <v>1241</v>
       </c>
       <c r="F288" s="4" t="s">
         <v>79</v>
@@ -11682,13 +11685,13 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292" s="35" t="s">
+        <v>621</v>
+      </c>
+      <c r="B292" s="35" t="s">
+        <v>622</v>
+      </c>
+      <c r="C292" s="35" t="s">
         <v>623</v>
-      </c>
-      <c r="B292" s="35" t="s">
-        <v>624</v>
-      </c>
-      <c r="C292" s="35" t="s">
-        <v>625</v>
       </c>
       <c r="D292" s="36" t="s">
         <v>307</v>
@@ -11742,19 +11745,19 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A295" s="35" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B295" s="35" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C295" s="35" t="s">
         <v>1387</v>
       </c>
-      <c r="B295" s="35" t="s">
+      <c r="D295" s="36" t="s">
         <v>1388</v>
       </c>
-      <c r="C295" s="35" t="s">
+      <c r="E295" s="37" t="s">
         <v>1389</v>
-      </c>
-      <c r="D295" s="36" t="s">
-        <v>1390</v>
-      </c>
-      <c r="E295" s="37" t="s">
-        <v>1391</v>
       </c>
       <c r="F295" s="35" t="s">
         <v>79</v>
@@ -11762,19 +11765,19 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296" s="35" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B296" s="35" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C296" s="35" t="s">
         <v>1053</v>
       </c>
-      <c r="B296" s="35" t="s">
+      <c r="D296" s="36" t="s">
         <v>1054</v>
       </c>
-      <c r="C296" s="35" t="s">
+      <c r="E296" s="37" t="s">
         <v>1055</v>
-      </c>
-      <c r="D296" s="36" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E296" s="37" t="s">
-        <v>1057</v>
       </c>
       <c r="F296" s="35" t="s">
         <v>79</v>
@@ -11822,13 +11825,13 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299" s="35" t="s">
+        <v>830</v>
+      </c>
+      <c r="B299" s="35" t="s">
+        <v>831</v>
+      </c>
+      <c r="C299" s="35" t="s">
         <v>832</v>
-      </c>
-      <c r="B299" s="35" t="s">
-        <v>833</v>
-      </c>
-      <c r="C299" s="35" t="s">
-        <v>834</v>
       </c>
       <c r="D299" s="36" t="s">
         <v>470</v>
@@ -11842,13 +11845,13 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" s="35" t="s">
+        <v>995</v>
+      </c>
+      <c r="B300" s="35" t="s">
+        <v>996</v>
+      </c>
+      <c r="C300" s="35" t="s">
         <v>997</v>
-      </c>
-      <c r="B300" s="35" t="s">
-        <v>998</v>
-      </c>
-      <c r="C300" s="35" t="s">
-        <v>999</v>
       </c>
       <c r="D300" s="36" t="s">
         <v>470</v>
@@ -11862,13 +11865,13 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A301" s="35" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B301" s="35" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C301" s="35" t="s">
         <v>1042</v>
-      </c>
-      <c r="B301" s="35" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C301" s="35" t="s">
-        <v>1044</v>
       </c>
       <c r="D301" s="36" t="s">
         <v>470</v>
@@ -11882,13 +11885,13 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302" s="35" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B302" s="35" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C302" s="35" t="s">
         <v>1106</v>
-      </c>
-      <c r="B302" s="35" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C302" s="35" t="s">
-        <v>1108</v>
       </c>
       <c r="D302" s="36" t="s">
         <v>470</v>
@@ -11902,13 +11905,13 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A303" s="35" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B303" s="35" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C303" s="35" t="s">
         <v>1132</v>
-      </c>
-      <c r="B303" s="35" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C303" s="35" t="s">
-        <v>1134</v>
       </c>
       <c r="D303" s="36" t="s">
         <v>470</v>
@@ -11922,13 +11925,13 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304" s="35" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B304" s="35" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C304" s="35" t="s">
         <v>1139</v>
-      </c>
-      <c r="B304" s="35" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C304" s="35" t="s">
-        <v>1141</v>
       </c>
       <c r="D304" s="36" t="s">
         <v>470</v>
@@ -11942,13 +11945,13 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="35" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="B305" s="35" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="C305" s="35" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="D305" s="36" t="s">
         <v>470</v>
@@ -11962,19 +11965,19 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="C306" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="B306" s="4" t="s">
+      <c r="D306" s="46" t="s">
         <v>676</v>
       </c>
-      <c r="C306" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="D306" s="46" t="s">
-        <v>678</v>
-      </c>
       <c r="E306" s="4" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F306" s="4" t="s">
         <v>42</v>
@@ -11982,42 +11985,42 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C307" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="B307" s="4" t="s">
+      <c r="D307" s="46" t="s">
         <v>671</v>
       </c>
-      <c r="C307" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="D307" s="46" t="s">
-        <v>673</v>
-      </c>
       <c r="E307" s="4" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H307" s="44" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C308" s="4" t="s">
         <v>1287</v>
       </c>
-      <c r="B308" s="4" t="s">
+      <c r="D308" s="46" t="s">
         <v>1288</v>
       </c>
-      <c r="C308" s="4" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D308" s="46" t="s">
-        <v>1290</v>
-      </c>
       <c r="E308" s="4" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="F308" s="4" t="s">
         <v>42</v>
@@ -12085,19 +12088,19 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C312" s="4" t="s">
         <v>1245</v>
       </c>
-      <c r="B312" s="4" t="s">
+      <c r="D312" s="46" t="s">
         <v>1246</v>
       </c>
-      <c r="C312" s="4" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D312" s="46" t="s">
-        <v>1248</v>
-      </c>
       <c r="E312" s="4" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="F312" s="4" t="s">
         <v>42</v>
@@ -12105,19 +12108,19 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="4" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D313" s="46" t="s">
         <v>1440</v>
       </c>
-      <c r="B313" s="4" t="s">
-        <v>1441</v>
-      </c>
-      <c r="C313" s="4" t="s">
-        <v>1442</v>
-      </c>
-      <c r="D313" s="46" t="s">
-        <v>1443</v>
-      </c>
       <c r="E313" s="4" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="F313" s="4" t="s">
         <v>42</v>
@@ -12125,19 +12128,19 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B314" s="45" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C314" s="4" t="s">
         <v>1037</v>
       </c>
-      <c r="B314" s="45" t="s">
+      <c r="D314" s="46" t="s">
         <v>1038</v>
       </c>
-      <c r="C314" s="4" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D314" s="46" t="s">
-        <v>1040</v>
-      </c>
       <c r="E314" s="4" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="F314" s="4" t="s">
         <v>42</v>
@@ -12145,19 +12148,19 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="4" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B315" s="45" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C315" s="4" t="s">
         <v>1205</v>
       </c>
-      <c r="B315" s="45" t="s">
+      <c r="D315" s="46" t="s">
         <v>1206</v>
       </c>
-      <c r="C315" s="4" t="s">
-        <v>1207</v>
-      </c>
-      <c r="D315" s="46" t="s">
-        <v>1208</v>
-      </c>
       <c r="E315" s="4" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="F315" s="4" t="s">
         <v>42</v>
@@ -12165,19 +12168,19 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="C316" s="4" t="s">
         <v>818</v>
       </c>
-      <c r="B316" s="4" t="s">
+      <c r="D316" s="46" t="s">
         <v>819</v>
       </c>
-      <c r="C316" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="D316" s="46" t="s">
-        <v>821</v>
-      </c>
       <c r="E316" s="4" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="F316" s="4" t="s">
         <v>42</v>
@@ -12185,19 +12188,19 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="4" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C317" s="4" t="s">
         <v>1383</v>
       </c>
-      <c r="B317" s="4" t="s">
+      <c r="D317" s="46" t="s">
         <v>1384</v>
       </c>
-      <c r="C317" s="4" t="s">
-        <v>1385</v>
-      </c>
-      <c r="D317" s="46" t="s">
-        <v>1386</v>
-      </c>
       <c r="E317" s="4" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="F317" s="4" t="s">
         <v>42</v>
@@ -12205,19 +12208,19 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="C318" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="B318" s="4" t="s">
+      <c r="D318" s="46" t="s">
         <v>899</v>
       </c>
-      <c r="C318" s="4" t="s">
-        <v>900</v>
-      </c>
-      <c r="D318" s="46" t="s">
-        <v>901</v>
-      </c>
       <c r="E318" s="4" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="F318" s="4" t="s">
         <v>42</v>
@@ -12225,19 +12228,19 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="C319" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="B319" s="4" t="s">
+      <c r="D319" s="46" t="s">
         <v>635</v>
       </c>
-      <c r="C319" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="D319" s="46" t="s">
-        <v>637</v>
-      </c>
       <c r="E319" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F319" s="4" t="s">
         <v>42</v>
@@ -12265,19 +12268,19 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="C321" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="B321" s="4" t="s">
+      <c r="D321" s="46" t="s">
         <v>639</v>
       </c>
-      <c r="C321" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="D321" s="46" t="s">
-        <v>641</v>
-      </c>
       <c r="E321" s="4" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F321" s="4" t="s">
         <v>42</v>
@@ -12285,19 +12288,19 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C322" s="4" t="s">
         <v>1073</v>
       </c>
-      <c r="B322" s="4" t="s">
+      <c r="D322" s="46" t="s">
         <v>1074</v>
       </c>
-      <c r="C322" s="4" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D322" s="46" t="s">
-        <v>1076</v>
-      </c>
       <c r="E322" s="4" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F322" s="4" t="s">
         <v>42</v>
@@ -12305,19 +12308,19 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A323" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C323" s="4" t="s">
         <v>1256</v>
       </c>
-      <c r="B323" s="4" t="s">
+      <c r="D323" s="46" t="s">
         <v>1257</v>
       </c>
-      <c r="C323" s="4" t="s">
-        <v>1258</v>
-      </c>
-      <c r="D323" s="46" t="s">
-        <v>1259</v>
-      </c>
       <c r="E323" s="4" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="F323" s="4" t="s">
         <v>42</v>
@@ -12365,19 +12368,19 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C326" s="4" t="s">
         <v>1148</v>
       </c>
-      <c r="B326" s="4" t="s">
+      <c r="D326" s="46" t="s">
         <v>1149</v>
       </c>
-      <c r="C326" s="4" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D326" s="46" t="s">
-        <v>1151</v>
-      </c>
       <c r="E326" s="4" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="F326" s="4" t="s">
         <v>42</v>
@@ -12405,19 +12408,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A328" s="4" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C328" s="4" t="s">
         <v>1228</v>
       </c>
-      <c r="B328" s="4" t="s">
+      <c r="D328" s="46" t="s">
         <v>1229</v>
       </c>
-      <c r="C328" s="4" t="s">
-        <v>1230</v>
-      </c>
-      <c r="D328" s="46" t="s">
-        <v>1231</v>
-      </c>
       <c r="E328" s="4" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="F328" s="4" t="s">
         <v>42</v>
@@ -12425,19 +12428,19 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A329" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C329" s="4" t="s">
         <v>1135</v>
       </c>
-      <c r="B329" s="4" t="s">
+      <c r="D329" s="46" t="s">
         <v>1136</v>
       </c>
-      <c r="C329" s="4" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D329" s="46" t="s">
-        <v>1138</v>
-      </c>
       <c r="E329" s="4" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="F329" s="4" t="s">
         <v>42</v>
@@ -12445,19 +12448,19 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A330" s="4" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C330" s="4" t="s">
         <v>1305</v>
       </c>
-      <c r="B330" s="4" t="s">
+      <c r="D330" s="46" t="s">
         <v>1306</v>
       </c>
-      <c r="C330" s="4" t="s">
-        <v>1307</v>
-      </c>
-      <c r="D330" s="46" t="s">
-        <v>1308</v>
-      </c>
       <c r="E330" s="4" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>42</v>
@@ -12485,19 +12488,19 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C332" s="4" t="s">
         <v>1197</v>
       </c>
-      <c r="B332" s="4" t="s">
+      <c r="D332" s="46" t="s">
         <v>1198</v>
       </c>
-      <c r="C332" s="4" t="s">
-        <v>1199</v>
-      </c>
-      <c r="D332" s="46" t="s">
-        <v>1200</v>
-      </c>
       <c r="E332" s="4" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="F332" s="4" t="s">
         <v>42</v>
@@ -12505,19 +12508,19 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A333" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C333" s="4" t="s">
         <v>1340</v>
       </c>
-      <c r="B333" s="4" t="s">
+      <c r="D333" s="46" t="s">
         <v>1341</v>
       </c>
-      <c r="C333" s="4" t="s">
-        <v>1342</v>
-      </c>
-      <c r="D333" s="46" t="s">
-        <v>1343</v>
-      </c>
       <c r="E333" s="4" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="F333" s="4" t="s">
         <v>42</v>
@@ -12545,19 +12548,19 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A335" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="C335" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="B335" s="4" t="s">
+      <c r="D335" s="46" t="s">
         <v>789</v>
       </c>
-      <c r="C335" s="4" t="s">
-        <v>790</v>
-      </c>
-      <c r="D335" s="46" t="s">
-        <v>791</v>
-      </c>
       <c r="E335" s="4" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="F335" s="4" t="s">
         <v>42</v>
@@ -12565,19 +12568,19 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A336" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="C336" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="B336" s="4" t="s">
+      <c r="D336" s="46" t="s">
         <v>785</v>
       </c>
-      <c r="C336" s="4" t="s">
-        <v>786</v>
-      </c>
-      <c r="D336" s="46" t="s">
-        <v>787</v>
-      </c>
       <c r="E336" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="F336" s="4" t="s">
         <v>42</v>
@@ -12585,19 +12588,19 @@
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A337" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C337" s="4" t="s">
         <v>1087</v>
       </c>
-      <c r="B337" s="4" t="s">
+      <c r="D337" s="46" t="s">
         <v>1088</v>
       </c>
-      <c r="C337" s="4" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D337" s="46" t="s">
-        <v>1090</v>
-      </c>
       <c r="E337" s="4" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="F337" s="4" t="s">
         <v>42</v>
@@ -12605,19 +12608,19 @@
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D338" s="46" t="s">
         <v>1436</v>
       </c>
-      <c r="B338" s="4" t="s">
-        <v>1437</v>
-      </c>
-      <c r="C338" s="4" t="s">
-        <v>1438</v>
-      </c>
-      <c r="D338" s="46" t="s">
-        <v>1439</v>
-      </c>
       <c r="E338" s="4" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="F338" s="4" t="s">
         <v>42</v>
@@ -12625,19 +12628,19 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339" s="4" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C339" s="4" t="s">
         <v>1283</v>
       </c>
-      <c r="B339" s="4" t="s">
+      <c r="D339" s="46" t="s">
         <v>1284</v>
       </c>
-      <c r="C339" s="4" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D339" s="46" t="s">
-        <v>1286</v>
-      </c>
       <c r="E339" s="4" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F339" s="4" t="s">
         <v>42</v>
@@ -12665,19 +12668,19 @@
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A341" s="4" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B341" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C341" s="4" t="s">
         <v>1294</v>
       </c>
-      <c r="B341" s="4" t="s">
+      <c r="D341" s="46" t="s">
         <v>1295</v>
       </c>
-      <c r="C341" s="4" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D341" s="46" t="s">
-        <v>1297</v>
-      </c>
       <c r="E341" s="4" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="F341" s="4" t="s">
         <v>42</v>
@@ -12685,19 +12688,19 @@
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="C342" s="4" t="s">
         <v>938</v>
       </c>
-      <c r="B342" s="4" t="s">
+      <c r="D342" s="46" t="s">
         <v>939</v>
       </c>
-      <c r="C342" s="4" t="s">
-        <v>940</v>
-      </c>
-      <c r="D342" s="46" t="s">
-        <v>941</v>
-      </c>
       <c r="E342" s="4" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="F342" s="4" t="s">
         <v>42</v>
@@ -12765,19 +12768,19 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A346" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="C346" s="4" t="s">
         <v>907</v>
       </c>
-      <c r="B346" s="4" t="s">
+      <c r="D346" s="46" t="s">
         <v>908</v>
       </c>
-      <c r="C346" s="4" t="s">
-        <v>909</v>
-      </c>
-      <c r="D346" s="46" t="s">
-        <v>910</v>
-      </c>
       <c r="E346" s="4" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="F346" s="4" t="s">
         <v>42</v>
@@ -12786,19 +12789,19 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A347" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="B347" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="C347" s="4" t="s">
         <v>969</v>
       </c>
-      <c r="B347" s="4" t="s">
+      <c r="D347" s="46" t="s">
         <v>970</v>
       </c>
-      <c r="C347" s="4" t="s">
-        <v>971</v>
-      </c>
-      <c r="D347" s="46" t="s">
-        <v>972</v>
-      </c>
       <c r="E347" s="4" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="F347" s="4" t="s">
         <v>42</v>
@@ -12807,19 +12810,19 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A348" s="4" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B348" s="4" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C348" s="4" t="s">
         <v>1201</v>
       </c>
-      <c r="B348" s="4" t="s">
+      <c r="D348" s="46" t="s">
         <v>1202</v>
       </c>
-      <c r="C348" s="4" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D348" s="46" t="s">
-        <v>1204</v>
-      </c>
       <c r="E348" s="4" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="F348" s="4" t="s">
         <v>42</v>
@@ -12828,19 +12831,19 @@
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A349" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B349" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D349" s="46" t="s">
         <v>1431</v>
       </c>
-      <c r="B349" s="4" t="s">
+      <c r="E349" s="4" t="s">
         <v>1432</v>
-      </c>
-      <c r="C349" s="4" t="s">
-        <v>1433</v>
-      </c>
-      <c r="D349" s="46" t="s">
-        <v>1434</v>
-      </c>
-      <c r="E349" s="4" t="s">
-        <v>1435</v>
       </c>
       <c r="F349" s="4" t="s">
         <v>42</v>
@@ -12849,19 +12852,19 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A350" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B350" s="4" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D350" s="46" t="s">
         <v>1431</v>
       </c>
-      <c r="B350" s="4" t="s">
-        <v>1453</v>
-      </c>
-      <c r="C350" s="4" t="s">
-        <v>1454</v>
-      </c>
-      <c r="D350" s="46" t="s">
-        <v>1434</v>
-      </c>
       <c r="E350" s="4" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="F350" s="4" t="s">
         <v>42</v>
@@ -12891,19 +12894,19 @@
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A352" s="4" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C352" s="4" t="s">
         <v>1249</v>
       </c>
-      <c r="B352" s="4" t="s">
+      <c r="D352" s="46" t="s">
         <v>1250</v>
       </c>
-      <c r="C352" s="4" t="s">
-        <v>1251</v>
-      </c>
-      <c r="D352" s="46" t="s">
-        <v>1252</v>
-      </c>
       <c r="E352" s="4" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="F352" s="4" t="s">
         <v>42</v>
@@ -12912,19 +12915,19 @@
     </row>
     <row r="353" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A353" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C353" s="4" t="s">
         <v>1177</v>
       </c>
-      <c r="B353" s="4" t="s">
+      <c r="D353" s="46" t="s">
         <v>1178</v>
       </c>
-      <c r="C353" s="4" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D353" s="46" t="s">
-        <v>1180</v>
-      </c>
       <c r="E353" s="4" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="F353" s="4" t="s">
         <v>42</v>
@@ -12933,19 +12936,19 @@
     </row>
     <row r="354" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A354" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C354" s="4" t="s">
         <v>1376</v>
       </c>
-      <c r="B354" s="4" t="s">
+      <c r="D354" s="46" t="s">
         <v>1377</v>
       </c>
-      <c r="C354" s="4" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D354" s="46" t="s">
-        <v>1379</v>
-      </c>
       <c r="E354" s="4" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="F354" s="4" t="s">
         <v>42</v>
@@ -12975,19 +12978,19 @@
     </row>
     <row r="356" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A356" s="4" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D356" s="46" t="s">
         <v>1461</v>
       </c>
-      <c r="B356" s="4" t="s">
-        <v>1462</v>
-      </c>
-      <c r="C356" s="4" t="s">
-        <v>1463</v>
-      </c>
-      <c r="D356" s="46" t="s">
-        <v>1464</v>
-      </c>
       <c r="E356" s="4" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="F356" s="4" t="s">
         <v>42</v>
@@ -13065,19 +13068,19 @@
     </row>
     <row r="360" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A360" s="4" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C360" s="4" t="s">
         <v>1215</v>
       </c>
-      <c r="B360" s="4" t="s">
+      <c r="D360" s="46" t="s">
         <v>1216</v>
       </c>
-      <c r="C360" s="4" t="s">
+      <c r="E360" s="4" t="s">
         <v>1217</v>
-      </c>
-      <c r="D360" s="46" t="s">
-        <v>1218</v>
-      </c>
-      <c r="E360" s="4" t="s">
-        <v>1219</v>
       </c>
       <c r="F360" s="4" t="s">
         <v>42</v>
@@ -13087,19 +13090,19 @@
     </row>
     <row r="361" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A361" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="C361" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="B361" s="4" t="s">
+      <c r="D361" s="46" t="s">
         <v>631</v>
       </c>
-      <c r="C361" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="D361" s="46" t="s">
-        <v>633</v>
-      </c>
       <c r="E361" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F361" s="4" t="s">
         <v>42</v>
@@ -13108,19 +13111,19 @@
     </row>
     <row r="362" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A362" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="C362" s="4" t="s">
         <v>803</v>
       </c>
-      <c r="B362" s="4" t="s">
+      <c r="D362" s="46" t="s">
         <v>804</v>
       </c>
-      <c r="C362" s="4" t="s">
-        <v>805</v>
-      </c>
-      <c r="D362" s="46" t="s">
-        <v>806</v>
-      </c>
       <c r="E362" s="4" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="F362" s="4" t="s">
         <v>42</v>
@@ -13129,40 +13132,40 @@
     </row>
     <row r="363" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
+        <v>684</v>
+      </c>
+      <c r="B363" s="17" t="s">
+        <v>685</v>
+      </c>
+      <c r="C363" t="s">
         <v>686</v>
       </c>
-      <c r="B363" s="17" t="s">
+      <c r="D363" s="15" t="s">
         <v>687</v>
       </c>
-      <c r="C363" t="s">
-        <v>688</v>
-      </c>
-      <c r="D363" s="15" t="s">
-        <v>689</v>
-      </c>
       <c r="E363" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="364" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A364" s="28"/>
       <c r="B364" s="28" t="s">
+        <v>685</v>
+      </c>
+      <c r="C364" s="28" t="s">
+        <v>688</v>
+      </c>
+      <c r="D364" s="15" t="s">
         <v>687</v>
       </c>
-      <c r="C364" s="28" t="s">
-        <v>690</v>
-      </c>
-      <c r="D364" s="15" t="s">
+      <c r="E364" t="s">
+        <v>686</v>
+      </c>
+      <c r="F364" t="s">
+        <v>18</v>
+      </c>
+      <c r="I364" t="s">
         <v>689</v>
-      </c>
-      <c r="E364" t="s">
-        <v>688</v>
-      </c>
-      <c r="F364" t="s">
-        <v>18</v>
-      </c>
-      <c r="I364" t="s">
-        <v>691</v>
       </c>
       <c r="N364" s="7"/>
       <c r="O364" s="5"/>
@@ -13203,19 +13206,19 @@
     </row>
     <row r="367" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A367" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B367" s="17" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C367" t="s">
         <v>1309</v>
       </c>
-      <c r="B367" s="17" t="s">
+      <c r="D367" s="15" t="s">
         <v>1310</v>
       </c>
-      <c r="C367" t="s">
-        <v>1311</v>
-      </c>
-      <c r="D367" s="15" t="s">
-        <v>1312</v>
-      </c>
       <c r="E367" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="368" spans="1:17" x14ac:dyDescent="0.2">
@@ -13245,19 +13248,19 @@
     </row>
     <row r="369" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B369" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C369" t="s">
         <v>1355</v>
       </c>
-      <c r="B369" t="s">
+      <c r="D369" s="15" t="s">
         <v>1356</v>
       </c>
-      <c r="C369" t="s">
-        <v>1357</v>
-      </c>
-      <c r="D369" s="15" t="s">
-        <v>1358</v>
-      </c>
       <c r="E369" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="F369" t="s">
         <v>157</v>
@@ -13270,19 +13273,19 @@
     </row>
     <row r="370" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A370" s="4" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D370" s="15" t="s">
         <v>1425</v>
       </c>
-      <c r="B370" s="4" t="s">
-        <v>1426</v>
-      </c>
-      <c r="C370" s="4" t="s">
-        <v>1427</v>
-      </c>
-      <c r="D370" s="15" t="s">
-        <v>1428</v>
-      </c>
       <c r="E370" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="F370" t="s">
         <v>157</v>
@@ -13389,19 +13392,19 @@
     </row>
     <row r="375" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A375" s="4" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C375" s="4" t="s">
         <v>1184</v>
       </c>
-      <c r="B375" s="4" t="s">
+      <c r="D375" s="15" t="s">
         <v>1185</v>
       </c>
-      <c r="C375" s="4" t="s">
-        <v>1186</v>
-      </c>
-      <c r="D375" s="15" t="s">
-        <v>1187</v>
-      </c>
       <c r="E375" s="4" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="F375" t="s">
         <v>18</v>
@@ -13412,36 +13415,36 @@
     </row>
     <row r="376" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B376" s="17" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C376" t="s">
         <v>1184</v>
       </c>
-      <c r="B376" s="17" t="s">
+      <c r="D376" s="15" t="s">
         <v>1185</v>
       </c>
-      <c r="C376" t="s">
-        <v>1186</v>
-      </c>
-      <c r="D376" s="15" t="s">
-        <v>1187</v>
-      </c>
       <c r="E376" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="377" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A377" s="4" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C377" s="4" t="s">
         <v>1188</v>
       </c>
-      <c r="B377" s="4" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C377" s="4" t="s">
-        <v>1190</v>
-      </c>
       <c r="D377" s="15" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="E377" s="4" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="F377" t="s">
         <v>18</v>
@@ -13452,19 +13455,19 @@
     </row>
     <row r="378" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A378" s="4" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C378" s="4" t="s">
         <v>1191</v>
       </c>
-      <c r="B378" s="4" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C378" s="4" t="s">
-        <v>1193</v>
-      </c>
       <c r="D378" s="15" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="E378" s="4" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="F378" t="s">
         <v>18</v>
@@ -13475,19 +13478,19 @@
     </row>
     <row r="379" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A379" s="4" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C379" s="4" t="s">
         <v>1194</v>
       </c>
-      <c r="B379" s="4" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C379" s="4" t="s">
-        <v>1196</v>
-      </c>
       <c r="D379" s="15" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="E379" s="4" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="F379" t="s">
         <v>18</v>
@@ -13498,19 +13501,19 @@
     </row>
     <row r="380" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A380" s="4" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C380" s="4" t="s">
         <v>1212</v>
       </c>
-      <c r="B380" s="4" t="s">
-        <v>1213</v>
-      </c>
-      <c r="C380" s="4" t="s">
-        <v>1214</v>
-      </c>
       <c r="D380" s="15" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="E380" s="4" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="F380" t="s">
         <v>18</v>
@@ -13521,87 +13524,87 @@
     </row>
     <row r="381" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B381" s="17" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C381" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D381" s="15" t="s">
         <v>1475</v>
       </c>
-      <c r="B381" s="17" t="s">
-        <v>1476</v>
-      </c>
-      <c r="C381" t="s">
-        <v>1477</v>
-      </c>
-      <c r="D381" s="15" t="s">
-        <v>1478</v>
-      </c>
       <c r="E381" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="382" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
+        <v>886</v>
+      </c>
+      <c r="B382" s="17" t="s">
+        <v>887</v>
+      </c>
+      <c r="C382" t="s">
         <v>888</v>
       </c>
-      <c r="B382" s="17" t="s">
+      <c r="D382" s="15" t="s">
         <v>889</v>
       </c>
-      <c r="C382" t="s">
-        <v>890</v>
-      </c>
-      <c r="D382" s="15" t="s">
-        <v>891</v>
-      </c>
       <c r="E382" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="383" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
+        <v>775</v>
+      </c>
+      <c r="B383" s="17" t="s">
+        <v>776</v>
+      </c>
+      <c r="C383" t="s">
         <v>777</v>
       </c>
-      <c r="B383" s="17" t="s">
+      <c r="D383" s="15" t="s">
         <v>778</v>
       </c>
-      <c r="C383" t="s">
-        <v>779</v>
-      </c>
-      <c r="D383" s="15" t="s">
-        <v>780</v>
-      </c>
       <c r="E383" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="384" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B384" s="17" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C384" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D384" s="15" t="s">
         <v>1469</v>
       </c>
-      <c r="B384" s="17" t="s">
-        <v>1470</v>
-      </c>
-      <c r="C384" t="s">
-        <v>1471</v>
-      </c>
-      <c r="D384" s="15" t="s">
-        <v>1472</v>
-      </c>
       <c r="E384" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A385" s="4" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="D385" s="15" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="E385" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="F385" t="s">
         <v>18</v>
@@ -13612,33 +13615,33 @@
         <v>422</v>
       </c>
       <c r="B386" s="17" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C386" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D386" s="15" t="s">
         <v>1253</v>
       </c>
-      <c r="C386" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D386" s="15" t="s">
-        <v>1255</v>
-      </c>
       <c r="E386" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
+        <v>624</v>
+      </c>
+      <c r="B387" s="17" t="s">
+        <v>625</v>
+      </c>
+      <c r="C387" t="s">
         <v>626</v>
       </c>
-      <c r="B387" s="17" t="s">
+      <c r="D387" s="15" t="s">
         <v>627</v>
       </c>
-      <c r="C387" t="s">
-        <v>628</v>
-      </c>
-      <c r="D387" s="15" t="s">
-        <v>629</v>
-      </c>
       <c r="E387" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.2">
@@ -13691,16 +13694,16 @@
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B391" s="17" t="s">
+        <v>841</v>
+      </c>
+      <c r="C391" t="s">
+        <v>842</v>
+      </c>
+      <c r="D391" s="15" t="s">
         <v>843</v>
       </c>
-      <c r="C391" t="s">
-        <v>844</v>
-      </c>
-      <c r="D391" s="15" t="s">
-        <v>845</v>
-      </c>
       <c r="E391" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.2">
@@ -13747,16 +13750,16 @@
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B395" s="17" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C395" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D395" s="15" t="s">
         <v>1045</v>
       </c>
-      <c r="C395" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D395" s="15" t="s">
-        <v>1047</v>
-      </c>
       <c r="E395" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.2">
@@ -13775,16 +13778,16 @@
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B397" t="s">
+        <v>693</v>
+      </c>
+      <c r="C397" t="s">
+        <v>694</v>
+      </c>
+      <c r="D397" s="15" t="s">
         <v>695</v>
       </c>
-      <c r="C397" t="s">
-        <v>696</v>
-      </c>
-      <c r="D397" s="15" t="s">
-        <v>697</v>
-      </c>
       <c r="E397" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.2">
@@ -13807,91 +13810,91 @@
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A399" s="35" t="s">
+        <v>864</v>
+      </c>
+      <c r="B399" s="41" t="s">
+        <v>865</v>
+      </c>
+      <c r="C399" s="35" t="s">
         <v>866</v>
       </c>
-      <c r="B399" s="41" t="s">
+      <c r="D399" s="42" t="s">
         <v>867</v>
       </c>
-      <c r="C399" s="35" t="s">
-        <v>868</v>
-      </c>
-      <c r="D399" s="42" t="s">
-        <v>869</v>
-      </c>
       <c r="E399" s="35" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="F399" s="37"/>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A400" s="35" t="s">
+        <v>868</v>
+      </c>
+      <c r="B400" s="41" t="s">
+        <v>869</v>
+      </c>
+      <c r="C400" s="35" t="s">
         <v>870</v>
       </c>
-      <c r="B400" s="41" t="s">
+      <c r="D400" s="42" t="s">
         <v>871</v>
       </c>
-      <c r="C400" s="35" t="s">
-        <v>872</v>
-      </c>
-      <c r="D400" s="42" t="s">
-        <v>873</v>
-      </c>
       <c r="E400" s="35" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="F400" s="37"/>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A401" s="35" t="s">
+        <v>872</v>
+      </c>
+      <c r="B401" s="41" t="s">
+        <v>873</v>
+      </c>
+      <c r="C401" s="35" t="s">
         <v>874</v>
       </c>
-      <c r="B401" s="41" t="s">
+      <c r="D401" s="42" t="s">
         <v>875</v>
       </c>
-      <c r="C401" s="35" t="s">
-        <v>876</v>
-      </c>
-      <c r="D401" s="42" t="s">
-        <v>877</v>
-      </c>
       <c r="E401" s="35" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="F401" s="37"/>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A402" s="35" t="s">
+        <v>914</v>
+      </c>
+      <c r="B402" s="41" t="s">
+        <v>915</v>
+      </c>
+      <c r="C402" s="35" t="s">
         <v>916</v>
       </c>
-      <c r="B402" s="41" t="s">
+      <c r="D402" s="42" t="s">
         <v>917</v>
       </c>
-      <c r="C402" s="35" t="s">
-        <v>918</v>
-      </c>
-      <c r="D402" s="42" t="s">
-        <v>919</v>
-      </c>
       <c r="E402" s="35" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="F402" s="37"/>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A403" s="35" t="s">
+        <v>860</v>
+      </c>
+      <c r="B403" s="41" t="s">
+        <v>861</v>
+      </c>
+      <c r="C403" s="37" t="s">
         <v>862</v>
       </c>
-      <c r="B403" s="41" t="s">
+      <c r="D403" s="42" t="s">
         <v>863</v>
       </c>
-      <c r="C403" s="37" t="s">
-        <v>864</v>
-      </c>
-      <c r="D403" s="42" t="s">
-        <v>865</v>
-      </c>
       <c r="E403" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F403" s="37"/>
     </row>
@@ -13929,42 +13932,42 @@
   <conditionalFormatting sqref="B319:B351">
     <cfRule type="duplicateValues" dxfId="11" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D129 D131:D190 D192:D355 D376:D1048576">
-    <cfRule type="containsBlanks" dxfId="10" priority="20">
+  <conditionalFormatting sqref="D131:D190 D192:D355 D376:D1048576 D1:D129">
+    <cfRule type="containsBlanks" dxfId="0" priority="20">
       <formula>LEN(TRIM(D1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D130">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D191">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D358:D359">
-    <cfRule type="containsBlanks" dxfId="7" priority="9">
+    <cfRule type="containsBlanks" dxfId="8" priority="9">
       <formula>LEN(TRIM(D358))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D360:D362 H357 D356 D366:D367 D375">
-    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D363:D365">
-    <cfRule type="containsBlanks" dxfId="5" priority="10">
+    <cfRule type="containsBlanks" dxfId="6" priority="10">
       <formula>LEN(TRIM(D363))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D368:D374">
-    <cfRule type="containsBlanks" dxfId="4" priority="2">
+    <cfRule type="containsBlanks" dxfId="5" priority="2">
       <formula>LEN(TRIM(D368))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E62">
-    <cfRule type="containsBlanks" dxfId="3" priority="33">
+    <cfRule type="containsBlanks" dxfId="4" priority="33">
       <formula>LEN(TRIM(E62))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H123">
-    <cfRule type="containsBlanks" dxfId="2" priority="27">
+    <cfRule type="containsBlanks" dxfId="3" priority="27">
       <formula>LEN(TRIM(H123))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13990,7 +13993,7 @@
   <sheetData>
     <row r="2" spans="1:6" s="13" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="B2" s="18"/>
     </row>
@@ -14005,13 +14008,13 @@
         <v>2</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -14025,110 +14028,110 @@
         <v>166</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="E5" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="24" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>165</v>
       </c>
       <c r="C6" s="24" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F6" t="s">
         <v>1485</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>1486</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="24" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>165</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="F7" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>165</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="F8" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>165</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="F9" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>165</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="F10" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -14142,203 +14145,203 @@
         <v>208</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="E11" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="24" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>207</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>207</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="24" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>207</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>207</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>1048</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="D16" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="E16" t="s">
         <v>1050</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E17" s="26" t="s">
         <v>1503</v>
       </c>
-      <c r="B17" s="24" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C17" s="24" t="s">
+      <c r="F17" s="26" t="s">
         <v>1504</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>1505</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>1506</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E18" s="26" t="s">
         <v>1508</v>
       </c>
-      <c r="B18" s="24" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>1509</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>1510</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>1511</v>
-      </c>
       <c r="F18" s="26" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="24" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="26"/>
       <c r="F20" s="26" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>1237</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="D21" s="23" t="s">
         <v>1238</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="E21" t="s">
         <v>1239</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>1240</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1241</v>
       </c>
       <c r="F21" t="s">
         <v>166</v>
@@ -14346,62 +14349,62 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="24" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E22" s="26" t="s">
         <v>1516</v>
       </c>
-      <c r="B22" s="24" t="s">
-        <v>1238</v>
-      </c>
-      <c r="C22" s="24" t="s">
+      <c r="F22" s="26" t="s">
         <v>1517</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>1518</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>1519</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="24" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -14441,27 +14444,27 @@
         <v>503</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>1118</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>1120</v>
-      </c>
       <c r="D27" s="22" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E27" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F27" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -14472,7 +14475,7 @@
         <v>305</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="D28" s="22" t="s">
         <v>307</v>
@@ -14481,83 +14484,83 @@
         <v>308</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="24" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="B29" s="24" t="s">
         <v>305</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="24" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="B30" s="24" t="s">
         <v>305</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="24" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="B31" s="24" t="s">
         <v>305</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
       <c r="D31" s="25"/>
       <c r="E31" s="26"/>
       <c r="F31" s="26" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>1387</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="D32" s="22" t="s">
         <v>1388</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="E32" t="s">
         <v>1389</v>
       </c>
-      <c r="D32" s="22" t="s">
-        <v>1390</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1391</v>
-      </c>
       <c r="F32" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -14577,47 +14580,47 @@
         <v>493</v>
       </c>
       <c r="F33" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="24" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="B34" s="24" t="s">
         <v>490</v>
       </c>
       <c r="C34" s="24" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F34" s="26" t="s">
         <v>1539</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>1540</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>1541</v>
-      </c>
-      <c r="F34" s="26" t="s">
-        <v>1542</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="24" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="B35" s="24" t="s">
         <v>490</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -14637,78 +14640,78 @@
         <v>598</v>
       </c>
       <c r="F36" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="26" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="24" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="B37" s="24" t="s">
         <v>595</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="38" spans="1:6" s="26" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="24" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="B38" s="24" t="s">
         <v>595</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>1053</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="D39" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="E39" t="s">
         <v>1055</v>
       </c>
-      <c r="D39" s="22" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1057</v>
-      </c>
       <c r="F39" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>623</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>625</v>
       </c>
       <c r="D40" s="22" t="s">
         <v>307</v>
@@ -14717,18 +14720,18 @@
         <v>308</v>
       </c>
       <c r="F40" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>1132</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>1134</v>
       </c>
       <c r="D41" s="22" t="s">
         <v>470</v>
@@ -14737,18 +14740,18 @@
         <v>471</v>
       </c>
       <c r="F41" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="D42" s="22" t="s">
         <v>470</v>
@@ -14757,7 +14760,7 @@
         <v>471</v>
       </c>
       <c r="F42" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -14777,7 +14780,7 @@
         <v>471</v>
       </c>
       <c r="F43" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
@@ -14797,18 +14800,18 @@
         <v>471</v>
       </c>
       <c r="F44" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>1139</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>1141</v>
       </c>
       <c r="D45" s="22" t="s">
         <v>470</v>
@@ -14817,18 +14820,18 @@
         <v>471</v>
       </c>
       <c r="F45" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="24" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="D46" s="25" t="s">
         <v>470</v>
@@ -14837,38 +14840,38 @@
         <v>471</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="D47" s="22" t="s">
         <v>643</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="E47" t="s">
         <v>644</v>
       </c>
-      <c r="D47" s="22" t="s">
-        <v>645</v>
-      </c>
-      <c r="E47" t="s">
-        <v>646</v>
-      </c>
       <c r="F47" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>1042</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>1044</v>
       </c>
       <c r="D48" s="22" t="s">
         <v>470</v>
@@ -14877,18 +14880,18 @@
         <v>471</v>
       </c>
       <c r="F48" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>832</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>833</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>834</v>
       </c>
       <c r="D49" s="22" t="s">
         <v>470</v>
@@ -14897,18 +14900,18 @@
         <v>471</v>
       </c>
       <c r="F49" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>997</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>998</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>999</v>
       </c>
       <c r="D50" s="22" t="s">
         <v>470</v>
@@ -14917,18 +14920,18 @@
         <v>471</v>
       </c>
       <c r="F50" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>1106</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>1108</v>
       </c>
       <c r="D51" s="22" t="s">
         <v>470</v>
@@ -14937,7 +14940,7 @@
         <v>471</v>
       </c>
       <c r="F51" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -14959,19 +14962,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>1232</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="D53" s="22" t="s">
         <v>1233</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="E53" t="s">
         <v>1234</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>1235</v>
-      </c>
-      <c r="E53" t="s">
-        <v>1236</v>
       </c>
       <c r="F53" t="s">
         <v>414</v>
@@ -14979,19 +14982,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>1412</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="D54" s="22" t="s">
         <v>1413</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="E54" t="s">
         <v>1414</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>1415</v>
-      </c>
-      <c r="E54" t="s">
-        <v>1416</v>
       </c>
       <c r="F54" t="s">
         <v>414</v>
@@ -15039,19 +15042,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>665</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="D57" s="22" t="s">
         <v>666</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="E57" t="s">
         <v>667</v>
-      </c>
-      <c r="D57" s="22" t="s">
-        <v>668</v>
-      </c>
-      <c r="E57" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -15071,18 +15074,18 @@
         <v>488</v>
       </c>
       <c r="F58" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>1103</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>1105</v>
       </c>
       <c r="D59" s="22" t="s">
         <v>487</v>
@@ -15091,27 +15094,27 @@
         <v>488</v>
       </c>
       <c r="F59" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="D60" s="22" t="s">
         <v>680</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>682</v>
-      </c>
       <c r="E60" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F60" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
@@ -15136,10 +15139,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B60">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D61">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
+    <cfRule type="containsBlanks" dxfId="1" priority="1">
       <formula>LEN(TRIM(D61))=0</formula>
     </cfRule>
   </conditionalFormatting>
